--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19689,6 +19689,16 @@
       </c>
       <c r="B253" t="n">
         <v>30.5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>42.1</v>
       </c>
     </row>
   </sheetData>
@@ -19702,7 +19712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B249"/>
+  <dimension ref="A1:B250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22167,6 +22177,16 @@
         <v>70.43000000000001</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>68.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B254"/>
+  <dimension ref="A1:B255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19699,6 +19699,16 @@
       </c>
       <c r="B254" t="n">
         <v>42.1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>53.45</v>
       </c>
     </row>
   </sheetData>
@@ -19712,7 +19722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B250"/>
+  <dimension ref="A1:B251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22187,6 +22197,16 @@
         <v>68.5</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>72.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B255"/>
+  <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19709,6 +19709,16 @@
       </c>
       <c r="B255" t="n">
         <v>53.45</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>47.165</v>
       </c>
     </row>
   </sheetData>
@@ -19722,7 +19732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22207,6 +22217,16 @@
         <v>72.22</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>69.54000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19719,6 +19719,16 @@
       </c>
       <c r="B256" t="n">
         <v>47.165</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>48.6</v>
       </c>
     </row>
   </sheetData>
@@ -19732,7 +19742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22227,6 +22237,16 @@
         <v>69.54000000000001</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>68.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19729,6 +19729,16 @@
       </c>
       <c r="B257" t="n">
         <v>48.6</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -19742,7 +19752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22247,6 +22257,14 @@
         <v>68.3</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B258"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19739,6 +19739,26 @@
       </c>
       <c r="B258" t="n">
         <v>52</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>51.43</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>51.43</v>
       </c>
     </row>
   </sheetData>
@@ -19752,7 +19772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B254"/>
+  <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22265,6 +22285,26 @@
       </c>
       <c r="B254" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -19772,7 +19772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22305,6 +22305,16 @@
         <v>69</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>69.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19759,6 +19759,16 @@
       </c>
       <c r="B260" t="n">
         <v>51.43</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -19772,7 +19782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22315,6 +22325,16 @@
         <v>69.06</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>71.70999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B261"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19769,6 +19769,16 @@
       </c>
       <c r="B261" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>48.3</v>
       </c>
     </row>
   </sheetData>
@@ -19782,7 +19792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B258"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22335,6 +22345,16 @@
         <v>71.70999999999999</v>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>70.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19779,6 +19779,16 @@
       </c>
       <c r="B262" t="n">
         <v>48.3</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>49.395</v>
       </c>
     </row>
   </sheetData>
@@ -19792,7 +19802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22355,6 +22365,16 @@
         <v>70.14</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>66.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19789,6 +19789,16 @@
       </c>
       <c r="B263" t="n">
         <v>49.395</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>49.7</v>
       </c>
     </row>
   </sheetData>
@@ -19802,7 +19812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22375,6 +22385,16 @@
         <v>66.53</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>67.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19799,6 +19799,26 @@
       </c>
       <c r="B264" t="n">
         <v>49.7</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -19812,7 +19832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B261"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22395,6 +22415,26 @@
         <v>67.25</v>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>67.25</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>67.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19819,6 +19819,16 @@
       </c>
       <c r="B266" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>49.65</v>
       </c>
     </row>
   </sheetData>
@@ -19832,7 +19842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22435,6 +22445,16 @@
         <v>67.25</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>68.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19829,6 +19829,16 @@
       </c>
       <c r="B267" t="n">
         <v>49.65</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>50.9</v>
       </c>
     </row>
   </sheetData>
@@ -19842,7 +19852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22455,6 +22465,16 @@
         <v>68.56</v>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>63.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19839,6 +19839,16 @@
       </c>
       <c r="B268" t="n">
         <v>50.9</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>53.62</v>
       </c>
     </row>
   </sheetData>
@@ -19852,7 +19862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22475,6 +22485,16 @@
         <v>63.85</v>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>64.59999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B269"/>
+  <dimension ref="A1:B270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19849,6 +19849,16 @@
       </c>
       <c r="B269" t="n">
         <v>53.62</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>59.75</v>
       </c>
     </row>
   </sheetData>
@@ -19862,7 +19872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22495,6 +22505,16 @@
         <v>64.59999999999999</v>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>62.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19859,6 +19859,16 @@
       </c>
       <c r="B270" t="n">
         <v>59.75</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>58.9</v>
       </c>
     </row>
   </sheetData>
@@ -19872,7 +19882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22515,6 +22525,16 @@
         <v>62.48</v>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>66.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B271"/>
+  <dimension ref="A1:B273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19869,6 +19869,26 @@
       </c>
       <c r="B271" t="n">
         <v>58.9</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>58.995</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>58.995</v>
       </c>
     </row>
   </sheetData>
@@ -19882,7 +19902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22535,6 +22555,26 @@
         <v>66.3</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>66.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19889,6 +19889,16 @@
       </c>
       <c r="B273" t="n">
         <v>58.995</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>56.2</v>
       </c>
     </row>
   </sheetData>
@@ -19902,7 +19912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22575,6 +22585,16 @@
         <v>66.3</v>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>67.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19899,6 +19899,16 @@
       </c>
       <c r="B274" t="n">
         <v>56.2</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>52.62</v>
       </c>
     </row>
   </sheetData>
@@ -19912,7 +19922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B271"/>
+  <dimension ref="A1:B272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22595,6 +22605,16 @@
         <v>67.95</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>69.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19909,6 +19909,16 @@
       </c>
       <c r="B275" t="n">
         <v>52.62</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>51.75</v>
       </c>
     </row>
   </sheetData>
@@ -19922,7 +19932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B272"/>
+  <dimension ref="A1:B273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22615,6 +22625,16 @@
         <v>69.78</v>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>69.09999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B276"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19919,6 +19919,16 @@
       </c>
       <c r="B276" t="n">
         <v>51.75</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>54.8</v>
       </c>
     </row>
   </sheetData>
@@ -19932,7 +19942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22635,6 +22645,16 @@
         <v>69.09999999999999</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>70.09999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19929,6 +19929,16 @@
       </c>
       <c r="B277" t="n">
         <v>54.8</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>53.55</v>
       </c>
     </row>
   </sheetData>
@@ -19942,7 +19952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22655,6 +22665,16 @@
         <v>70.09999999999999</v>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>70.15000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B278"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19939,6 +19939,26 @@
       </c>
       <c r="B278" t="n">
         <v>53.55</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>54.05</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>54.05</v>
       </c>
     </row>
   </sheetData>
@@ -19952,7 +19972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22675,6 +22695,26 @@
         <v>70.15000000000001</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>70.15000000000001</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>70.15000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19959,6 +19959,16 @@
       </c>
       <c r="B280" t="n">
         <v>54.05</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>55.99</v>
       </c>
     </row>
   </sheetData>
@@ -19972,7 +19982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22715,6 +22725,16 @@
         <v>70.15000000000001</v>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19969,6 +19969,16 @@
       </c>
       <c r="B281" t="n">
         <v>55.99</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>49.1</v>
       </c>
     </row>
   </sheetData>
@@ -19982,7 +19992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B278"/>
+  <dimension ref="A1:B279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22735,6 +22745,16 @@
         <v>72</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>71.15000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B282"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19979,6 +19979,16 @@
       </c>
       <c r="B282" t="n">
         <v>49.1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>46.7</v>
       </c>
     </row>
   </sheetData>
@@ -19992,7 +20002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B279"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22755,6 +22765,16 @@
         <v>71.15000000000001</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>71.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19989,6 +19989,16 @@
       </c>
       <c r="B283" t="n">
         <v>46.7</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>49.2</v>
       </c>
     </row>
   </sheetData>
@@ -20002,7 +20012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22775,6 +22785,16 @@
         <v>71.7</v>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>70.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B284"/>
+  <dimension ref="A1:B285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19999,6 +19999,16 @@
       </c>
       <c r="B284" t="n">
         <v>49.2</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>50.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B285"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20010,6 +20010,22 @@
       <c r="B285" t="n">
         <v>50.6</v>
       </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20026,6 +20026,16 @@
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>51.15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20035,6 +20035,16 @@
       </c>
       <c r="B288" t="n">
         <v>51.15</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>44.375</v>
       </c>
     </row>
   </sheetData>
@@ -20048,7 +20058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22831,6 +22841,16 @@
         <v>70.45</v>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>70.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20045,6 +20045,16 @@
       </c>
       <c r="B289" t="n">
         <v>44.375</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>43.16</v>
       </c>
     </row>
   </sheetData>
@@ -20058,7 +20068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B282"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22851,6 +22861,16 @@
         <v>70.75</v>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>71.70999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20055,6 +20055,16 @@
       </c>
       <c r="B290" t="n">
         <v>43.16</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>41.775</v>
       </c>
     </row>
   </sheetData>
@@ -20068,7 +20078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22871,6 +22881,16 @@
         <v>71.70999999999999</v>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>71.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20065,6 +20065,26 @@
       </c>
       <c r="B291" t="n">
         <v>41.775</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>42.55</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>42.55</v>
       </c>
     </row>
   </sheetData>
@@ -20078,7 +20098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B284"/>
+  <dimension ref="A1:B286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22891,6 +22911,26 @@
         <v>71.94</v>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>71.94</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>71.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20085,6 +20085,16 @@
       </c>
       <c r="B293" t="n">
         <v>42.55</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>45.2</v>
       </c>
     </row>
   </sheetData>
@@ -20098,7 +20108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22931,6 +22941,16 @@
         <v>71.94</v>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>71.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20095,6 +20095,16 @@
       </c>
       <c r="B294" t="n">
         <v>45.2</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>41.8</v>
       </c>
     </row>
   </sheetData>
@@ -20108,7 +20118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22951,6 +22961,16 @@
         <v>71.25</v>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>72.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20105,6 +20105,16 @@
       </c>
       <c r="B295" t="n">
         <v>41.8</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>40.21</v>
       </c>
     </row>
   </sheetData>
@@ -20118,7 +20128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22971,6 +22981,16 @@
         <v>72.95</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>72.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20115,6 +20115,16 @@
       </c>
       <c r="B296" t="n">
         <v>40.21</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>41.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20125,6 +20125,16 @@
       </c>
       <c r="B297" t="n">
         <v>41.35</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>38.4</v>
       </c>
     </row>
   </sheetData>
@@ -20138,7 +20148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23001,6 +23011,16 @@
         <v>72.8</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>76.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20135,6 +20135,26 @@
       </c>
       <c r="B298" t="n">
         <v>38.4</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>38.3</v>
       </c>
     </row>
   </sheetData>
@@ -20148,7 +20168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23021,6 +23041,26 @@
         <v>76.12</v>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>76.12</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>76.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20155,6 +20155,16 @@
       </c>
       <c r="B300" t="n">
         <v>38.3</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>38.885</v>
       </c>
     </row>
   </sheetData>
@@ -20168,7 +20178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B292"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23061,6 +23071,16 @@
         <v>76.12</v>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>74.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B301"/>
+  <dimension ref="A1:B302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20165,6 +20165,16 @@
       </c>
       <c r="B301" t="n">
         <v>38.885</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>41.535</v>
       </c>
     </row>
   </sheetData>
@@ -20178,7 +20188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23081,6 +23091,16 @@
         <v>74.5</v>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>73.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20175,6 +20175,16 @@
       </c>
       <c r="B302" t="n">
         <v>41.535</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>42.9</v>
       </c>
     </row>
   </sheetData>
@@ -20188,7 +20198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23101,6 +23111,16 @@
         <v>73.7</v>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B303"/>
+  <dimension ref="A1:B304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20185,6 +20185,16 @@
       </c>
       <c r="B303" t="n">
         <v>42.9</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>43.305</v>
       </c>
     </row>
   </sheetData>
@@ -20198,7 +20208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23121,6 +23131,16 @@
         <v>73</v>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>73.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B304"/>
+  <dimension ref="A1:B305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20195,6 +20195,16 @@
       </c>
       <c r="B304" t="n">
         <v>43.305</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>43.995</v>
       </c>
     </row>
   </sheetData>
@@ -20208,7 +20218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23141,6 +23151,16 @@
         <v>73.5</v>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>73.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B305"/>
+  <dimension ref="A1:B307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20205,6 +20205,26 @@
       </c>
       <c r="B305" t="n">
         <v>43.995</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>43.81</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>43.81</v>
       </c>
     </row>
   </sheetData>
@@ -20218,7 +20238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23161,6 +23181,26 @@
         <v>73.5</v>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>73.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B307"/>
+  <dimension ref="A1:B308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20225,6 +20225,16 @@
       </c>
       <c r="B307" t="n">
         <v>43.81</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>43.2</v>
       </c>
     </row>
   </sheetData>
@@ -20238,7 +20248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B299"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23201,6 +23211,16 @@
         <v>73.5</v>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>73.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -20248,7 +20248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23221,6 +23221,16 @@
         <v>73.5</v>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>73.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20235,6 +20235,16 @@
       </c>
       <c r="B308" t="n">
         <v>43.2</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>46.3</v>
       </c>
     </row>
   </sheetData>
@@ -20248,7 +20258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B301"/>
+  <dimension ref="A1:B302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23231,6 +23241,16 @@
         <v>73.75</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20245,6 +20245,16 @@
       </c>
       <c r="B309" t="n">
         <v>46.3</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -20258,7 +20268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23251,6 +23261,16 @@
         <v>71.8</v>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -17162,7 +17162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B310"/>
+  <dimension ref="A1:B311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20255,6 +20255,16 @@
       </c>
       <c r="B310" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>44.275</v>
       </c>
     </row>
   </sheetData>

--- a/data/epexspot_prices.xlsx
+++ b/data/epexspot_prices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GA25"/>
+  <dimension ref="A1:GB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1334,6 +1334,11 @@
           <t>31-oct.</t>
         </is>
       </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>17-mai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1993,6 +1998,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB2" t="n">
+        <v>130.37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2652,6 +2660,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB3" t="n">
+        <v>122.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3311,6 +3322,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB4" t="n">
+        <v>119.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3970,6 +3984,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB5" t="n">
+        <v>117.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4629,6 +4646,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB6" t="n">
+        <v>114.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5288,6 +5308,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB7" t="n">
+        <v>111.34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5947,6 +5970,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB8" t="n">
+        <v>109.21</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6606,6 +6632,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB9" t="n">
+        <v>103.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7265,6 +7294,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB10" t="n">
+        <v>90.44</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7924,6 +7956,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB11" t="n">
+        <v>50.91</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8583,6 +8618,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB12" t="n">
+        <v>8.18</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9242,6 +9280,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB13" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9901,6 +9942,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB14" t="n">
+        <v>6.24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10560,6 +10604,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11219,6 +11266,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB16" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11878,6 +11928,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB17" t="n">
+        <v>3.02</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12537,6 +12590,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB18" t="n">
+        <v>8.880000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13196,6 +13252,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB19" t="n">
+        <v>62.44</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13855,6 +13914,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB20" t="n">
+        <v>104.34</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14514,6 +14576,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB21" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15173,6 +15238,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB22" t="n">
+        <v>136.75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15832,6 +15900,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB23" t="n">
+        <v>136.11</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16491,6 +16562,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="GB24" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17149,6 +17223,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="GB25" t="n">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
